--- a/self_paced_reading/experiment/StimuliSPR.xlsx
+++ b/self_paced_reading/experiment/StimuliSPR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rubydowling/Documents/GitHub/AdjunctControl26/self_paced_reading/experiment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A813EE-F693-D54C-9337-E27F406F3C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E258177-F5BD-7042-A1D0-F51FAA6BE4BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2120" yWindow="760" windowWidth="27240" windowHeight="16180" xr2:uid="{49F68F50-C0A0-2A43-B5F6-E3A97D82E26C}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{49F68F50-C0A0-2A43-B5F6-E3A97D82E26C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="169">
   <si>
     <t>item</t>
   </si>
@@ -426,6 +426,123 @@
   </si>
   <si>
     <t>skyscraper</t>
+  </si>
+  <si>
+    <t>question_attribute</t>
+  </si>
+  <si>
+    <t>Was the brother mentioned in the sentence?</t>
+  </si>
+  <si>
+    <t>Will the baker present the Baked Alaska?</t>
+  </si>
+  <si>
+    <t>correct_answer</t>
+  </si>
+  <si>
+    <t>Was the car mentioned in the sentence?</t>
+  </si>
+  <si>
+    <t>Was the customer mentioned in the sentence?</t>
+  </si>
+  <si>
+    <t>Will the salesman market the skyscraper?</t>
+  </si>
+  <si>
+    <t>Was tennis mentioned in the sentence?</t>
+  </si>
+  <si>
+    <t>Were the girls mentioned in the sentence?</t>
+  </si>
+  <si>
+    <t>Was the queen mentioned in the sentence?</t>
+  </si>
+  <si>
+    <t>Will the chef abandon his station?</t>
+  </si>
+  <si>
+    <t>Was a gopher mentioned?</t>
+  </si>
+  <si>
+    <t>Was an athlete mentioned?</t>
+  </si>
+  <si>
+    <t>Was a woman mentioned?</t>
+  </si>
+  <si>
+    <t>Was a dog mentioned?</t>
+  </si>
+  <si>
+    <t>Was a wrecking ball mentioned?</t>
+  </si>
+  <si>
+    <t>Was a whale mentioned?</t>
+  </si>
+  <si>
+    <t>Was a librarian mentioned?</t>
+  </si>
+  <si>
+    <t>Was a parent mentioned?</t>
+  </si>
+  <si>
+    <t>Was a knight mentioned?</t>
+  </si>
+  <si>
+    <t>Was a writer mentioned?</t>
+  </si>
+  <si>
+    <t>Was a hammer mentioned?</t>
+  </si>
+  <si>
+    <t>Was a backpack mentioned?</t>
+  </si>
+  <si>
+    <t>Was a student mentioned?</t>
+  </si>
+  <si>
+    <t>Was a table mentioned?</t>
+  </si>
+  <si>
+    <t>Was a safe mentioned?</t>
+  </si>
+  <si>
+    <t>Was a coach mentioned?</t>
+  </si>
+  <si>
+    <t>Was a captain mentioned?</t>
+  </si>
+  <si>
+    <t>Was an assistant mentioned?</t>
+  </si>
+  <si>
+    <t>Was a  ball mentioned?</t>
+  </si>
+  <si>
+    <t>Was a engineer mentioned?</t>
+  </si>
+  <si>
+    <t>Was a cat mentioned?</t>
+  </si>
+  <si>
+    <t>Was a gala mentioned?</t>
+  </si>
+  <si>
+    <t>Was a basketball mentioned?</t>
+  </si>
+  <si>
+    <t>Will the author publish a new book?</t>
+  </si>
+  <si>
+    <t>Will the student study the tome poorly?</t>
+  </si>
+  <si>
+    <t>Are the teacher's classes easy?</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>NO</t>
   </si>
 </sst>
 </file>
@@ -804,16 +921,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1162B0D9-BC05-C945-B9C7-11028D0466E0}">
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="95.6640625" customWidth="1"/>
     <col min="5" max="5" width="17.1640625" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="7" width="26" customWidth="1"/>
+    <col min="8" max="8" width="48.33203125" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -835,8 +954,14 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -858,8 +983,14 @@
       <c r="G2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H2" t="s">
+        <v>164</v>
+      </c>
+      <c r="I2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -881,8 +1012,14 @@
       <c r="G3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H3" t="s">
+        <v>164</v>
+      </c>
+      <c r="I3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
@@ -904,8 +1041,14 @@
       <c r="G4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H4" t="s">
+        <v>164</v>
+      </c>
+      <c r="I4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
@@ -927,8 +1070,14 @@
       <c r="G5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H5" t="s">
+        <v>164</v>
+      </c>
+      <c r="I5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2</v>
       </c>
@@ -950,8 +1099,14 @@
       <c r="G6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H6" t="s">
+        <v>131</v>
+      </c>
+      <c r="I6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2</v>
       </c>
@@ -973,8 +1128,14 @@
       <c r="G7" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H7" t="s">
+        <v>131</v>
+      </c>
+      <c r="I7" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>2</v>
       </c>
@@ -996,8 +1157,14 @@
       <c r="G8" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H8" t="s">
+        <v>131</v>
+      </c>
+      <c r="I8" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>2</v>
       </c>
@@ -1019,8 +1186,14 @@
       <c r="G9" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H9" t="s">
+        <v>131</v>
+      </c>
+      <c r="I9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>3</v>
       </c>
@@ -1042,8 +1215,14 @@
       <c r="G10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H10" t="s">
+        <v>132</v>
+      </c>
+      <c r="I10" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>3</v>
       </c>
@@ -1065,8 +1244,14 @@
       <c r="G11" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H11" t="s">
+        <v>132</v>
+      </c>
+      <c r="I11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>3</v>
       </c>
@@ -1088,8 +1273,14 @@
       <c r="G12" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H12" t="s">
+        <v>132</v>
+      </c>
+      <c r="I12" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>3</v>
       </c>
@@ -1111,8 +1302,14 @@
       <c r="G13" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H13" t="s">
+        <v>132</v>
+      </c>
+      <c r="I13" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>4</v>
       </c>
@@ -1134,8 +1331,14 @@
       <c r="G14" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H14" t="s">
+        <v>165</v>
+      </c>
+      <c r="I14" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>4</v>
       </c>
@@ -1157,8 +1360,14 @@
       <c r="G15" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H15" t="s">
+        <v>165</v>
+      </c>
+      <c r="I15" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>4</v>
       </c>
@@ -1180,8 +1389,14 @@
       <c r="G16" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H16" t="s">
+        <v>165</v>
+      </c>
+      <c r="I16" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>4</v>
       </c>
@@ -1203,8 +1418,14 @@
       <c r="G17" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H17" t="s">
+        <v>165</v>
+      </c>
+      <c r="I17" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>5</v>
       </c>
@@ -1226,8 +1447,14 @@
       <c r="G18" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H18" t="s">
+        <v>134</v>
+      </c>
+      <c r="I18" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>5</v>
       </c>
@@ -1249,8 +1476,14 @@
       <c r="G19" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H19" t="s">
+        <v>134</v>
+      </c>
+      <c r="I19" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>5</v>
       </c>
@@ -1272,8 +1505,14 @@
       <c r="G20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H20" t="s">
+        <v>134</v>
+      </c>
+      <c r="I20" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>5</v>
       </c>
@@ -1295,8 +1534,14 @@
       <c r="G21" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H21" t="s">
+        <v>134</v>
+      </c>
+      <c r="I21" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>6</v>
       </c>
@@ -1318,8 +1563,14 @@
       <c r="G22" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H22" t="s">
+        <v>135</v>
+      </c>
+      <c r="I22" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>6</v>
       </c>
@@ -1341,8 +1592,14 @@
       <c r="G23" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H23" t="s">
+        <v>135</v>
+      </c>
+      <c r="I23" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>6</v>
       </c>
@@ -1364,8 +1621,14 @@
       <c r="G24" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H24" t="s">
+        <v>135</v>
+      </c>
+      <c r="I24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>6</v>
       </c>
@@ -1387,8 +1650,14 @@
       <c r="G25" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H25" t="s">
+        <v>135</v>
+      </c>
+      <c r="I25" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>7</v>
       </c>
@@ -1410,8 +1679,14 @@
       <c r="G26" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H26" t="s">
+        <v>136</v>
+      </c>
+      <c r="I26" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>7</v>
       </c>
@@ -1433,8 +1708,14 @@
       <c r="G27" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H27" t="s">
+        <v>136</v>
+      </c>
+      <c r="I27" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>7</v>
       </c>
@@ -1456,8 +1737,14 @@
       <c r="G28" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H28" t="s">
+        <v>136</v>
+      </c>
+      <c r="I28" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>7</v>
       </c>
@@ -1479,8 +1766,14 @@
       <c r="G29" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H29" t="s">
+        <v>136</v>
+      </c>
+      <c r="I29" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>8</v>
       </c>
@@ -1502,8 +1795,14 @@
       <c r="G30" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H30" t="s">
+        <v>137</v>
+      </c>
+      <c r="I30" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>8</v>
       </c>
@@ -1525,8 +1824,14 @@
       <c r="G31" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H31" t="s">
+        <v>137</v>
+      </c>
+      <c r="I31" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>8</v>
       </c>
@@ -1548,8 +1853,14 @@
       <c r="G32" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H32" t="s">
+        <v>137</v>
+      </c>
+      <c r="I32" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>8</v>
       </c>
@@ -1571,8 +1882,14 @@
       <c r="G33" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H33" t="s">
+        <v>137</v>
+      </c>
+      <c r="I33" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>9</v>
       </c>
@@ -1594,8 +1911,14 @@
       <c r="G34" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H34" t="s">
+        <v>138</v>
+      </c>
+      <c r="I34" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>9</v>
       </c>
@@ -1617,8 +1940,14 @@
       <c r="G35" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H35" t="s">
+        <v>138</v>
+      </c>
+      <c r="I35" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>9</v>
       </c>
@@ -1640,8 +1969,14 @@
       <c r="G36" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H36" t="s">
+        <v>138</v>
+      </c>
+      <c r="I36" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>9</v>
       </c>
@@ -1663,8 +1998,14 @@
       <c r="G37" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H37" t="s">
+        <v>138</v>
+      </c>
+      <c r="I37" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>10</v>
       </c>
@@ -1686,8 +2027,14 @@
       <c r="G38" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H38" t="s">
+        <v>166</v>
+      </c>
+      <c r="I38" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>10</v>
       </c>
@@ -1709,8 +2056,14 @@
       <c r="G39" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H39" t="s">
+        <v>166</v>
+      </c>
+      <c r="I39" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>10</v>
       </c>
@@ -1732,8 +2085,14 @@
       <c r="G40" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H40" t="s">
+        <v>166</v>
+      </c>
+      <c r="I40" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>10</v>
       </c>
@@ -1755,8 +2114,14 @@
       <c r="G41" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H41" t="s">
+        <v>166</v>
+      </c>
+      <c r="I41" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>11</v>
       </c>
@@ -1778,8 +2143,14 @@
       <c r="G42" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H42" t="s">
+        <v>139</v>
+      </c>
+      <c r="I42" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>11</v>
       </c>
@@ -1801,8 +2172,14 @@
       <c r="G43" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H43" t="s">
+        <v>139</v>
+      </c>
+      <c r="I43" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>11</v>
       </c>
@@ -1824,8 +2201,14 @@
       <c r="G44" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H44" t="s">
+        <v>139</v>
+      </c>
+      <c r="I44" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>11</v>
       </c>
@@ -1847,8 +2230,14 @@
       <c r="G45" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H45" t="s">
+        <v>139</v>
+      </c>
+      <c r="I45" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>12</v>
       </c>
@@ -1870,8 +2259,14 @@
       <c r="G46" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H46" t="s">
+        <v>140</v>
+      </c>
+      <c r="I46" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>12</v>
       </c>
@@ -1893,8 +2288,14 @@
       <c r="G47" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H47" t="s">
+        <v>140</v>
+      </c>
+      <c r="I47" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>12</v>
       </c>
@@ -1916,8 +2317,14 @@
       <c r="G48" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H48" t="s">
+        <v>140</v>
+      </c>
+      <c r="I48" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>12</v>
       </c>
@@ -1939,8 +2346,14 @@
       <c r="G49" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H49" t="s">
+        <v>140</v>
+      </c>
+      <c r="I49" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>1001</v>
       </c>
@@ -1956,8 +2369,14 @@
       <c r="E50" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H50" t="s">
+        <v>141</v>
+      </c>
+      <c r="I50" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>1002</v>
       </c>
@@ -1973,8 +2392,14 @@
       <c r="E51" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H51" t="s">
+        <v>142</v>
+      </c>
+      <c r="I51" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>1003</v>
       </c>
@@ -1990,8 +2415,14 @@
       <c r="E52" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H52" t="s">
+        <v>143</v>
+      </c>
+      <c r="I52" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>1004</v>
       </c>
@@ -2007,8 +2438,14 @@
       <c r="E53" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H53" t="s">
+        <v>144</v>
+      </c>
+      <c r="I53" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>1005</v>
       </c>
@@ -2024,8 +2461,14 @@
       <c r="E54" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H54" t="s">
+        <v>145</v>
+      </c>
+      <c r="I54" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>1006</v>
       </c>
@@ -2041,8 +2484,14 @@
       <c r="E55" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H55" t="s">
+        <v>146</v>
+      </c>
+      <c r="I55" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>1007</v>
       </c>
@@ -2058,8 +2507,14 @@
       <c r="E56" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H56" t="s">
+        <v>147</v>
+      </c>
+      <c r="I56" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>1008</v>
       </c>
@@ -2075,8 +2530,14 @@
       <c r="E57" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H57" t="s">
+        <v>148</v>
+      </c>
+      <c r="I57" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>1009</v>
       </c>
@@ -2092,8 +2553,14 @@
       <c r="E58" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H58" t="s">
+        <v>149</v>
+      </c>
+      <c r="I58" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>1010</v>
       </c>
@@ -2109,8 +2576,14 @@
       <c r="E59" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H59" t="s">
+        <v>150</v>
+      </c>
+      <c r="I59" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>1011</v>
       </c>
@@ -2126,8 +2599,14 @@
       <c r="E60" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H60" t="s">
+        <v>151</v>
+      </c>
+      <c r="I60" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>1012</v>
       </c>
@@ -2143,8 +2622,14 @@
       <c r="E61" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H61" t="s">
+        <v>152</v>
+      </c>
+      <c r="I61" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>1013</v>
       </c>
@@ -2160,8 +2645,14 @@
       <c r="E62" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H62" t="s">
+        <v>153</v>
+      </c>
+      <c r="I62" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>1014</v>
       </c>
@@ -2177,8 +2668,14 @@
       <c r="E63" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H63" t="s">
+        <v>154</v>
+      </c>
+      <c r="I63" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>1015</v>
       </c>
@@ -2194,8 +2691,14 @@
       <c r="E64" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="H64" t="s">
+        <v>155</v>
+      </c>
+      <c r="I64" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>1016</v>
       </c>
@@ -2211,8 +2714,14 @@
       <c r="E65" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="H65" t="s">
+        <v>156</v>
+      </c>
+      <c r="I65" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>1017</v>
       </c>
@@ -2228,8 +2737,14 @@
       <c r="E66" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="H66" t="s">
+        <v>157</v>
+      </c>
+      <c r="I66" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>1018</v>
       </c>
@@ -2245,8 +2760,14 @@
       <c r="E67" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="H67" t="s">
+        <v>143</v>
+      </c>
+      <c r="I67" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>1019</v>
       </c>
@@ -2262,8 +2783,14 @@
       <c r="E68" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="H68" t="s">
+        <v>158</v>
+      </c>
+      <c r="I68" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>1020</v>
       </c>
@@ -2279,8 +2806,14 @@
       <c r="E69" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="H69" t="s">
+        <v>159</v>
+      </c>
+      <c r="I69" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>1021</v>
       </c>
@@ -2296,8 +2829,14 @@
       <c r="E70" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="H70" t="s">
+        <v>160</v>
+      </c>
+      <c r="I70" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>1022</v>
       </c>
@@ -2313,8 +2852,14 @@
       <c r="E71" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="H71" t="s">
+        <v>161</v>
+      </c>
+      <c r="I71" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>1023</v>
       </c>
@@ -2330,8 +2875,14 @@
       <c r="E72" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="H72" t="s">
+        <v>162</v>
+      </c>
+      <c r="I72" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>1024</v>
       </c>
@@ -2346,6 +2897,12 @@
       </c>
       <c r="E73" t="s">
         <v>100</v>
+      </c>
+      <c r="H73" t="s">
+        <v>163</v>
+      </c>
+      <c r="I73" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
